--- a/docs/lightml/LEGAL_EVIDENCE_MASTER_MATRIX.xlsx
+++ b/docs/lightml/LEGAL_EVIDENCE_MASTER_MATRIX.xlsx
@@ -519,7 +519,7 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Evidence Completeness</t>
+          <t>Evidence Status</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Standard Employment Contract profile mapping required clauses.</t>
+          <t>An employment contract is an agreement under which an employee agrees to perform work under the direction and control of an employer in exchange for remuneration.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indonesian statute (UU) Art. UU No. 13 Tahun 2003 tentang Ketenagakerjaan sebagaimana diubah melalui UU No. 6 Tahun 2023, KUH Perdata (Indonesian Civil Code) Art. Pasal 1338, UU No. 30 Tahun 1999 tentang Arbitrase dan Alternatif Penyelesaian Sengketa, KUH Perdata (Indonesian Civil Code) Art. Pasal 1338, KUH Perdata (Indonesian Civil Code) Art. Pasal 1320, Pasal 1338,  Art. </t>
+          <t>KUH Perdata (Indonesian Civil Code) Article Pasal 1338, Indonesian statute (UU) Article UU No. 13 Tahun 2003 tentang Ketenagakerjaan sebagaimana diubah melalui UU No. 6 Tahun 2023, KUH Perdata (Indonesian Civil Code) Article Pasal 1320, Pasal 1338, KUH Perdata (Indonesian Civil Code) Article Pasal 1338, UU No. 30 Tahun 1999 tentang Arbitrase dan Alternatif Penyelesaian Sengketa</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>employment agreement, work agreement, labor contract, employment contract</t>
+          <t>employment contract, employment agreement, work agreement, labor contract</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Employment contract involves a relationship of subordination, fixed working hours, salary, and statutory protections, whereas consulting and service agreements involve independent contractors with no subordination.</t>
+          <t>An employment contract is legally characterized by subordination, placing the employee under the employer's direct control and supervision. It triggers mandatory statutory protections such as minimum wage, leave, severance, and social security. Conversely, consulting and service agreements establish independent contractor relationships, where the service provider retains operational autonomy, manages their own tools, and is not subject to employer disciplinary power.</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Evidence Not Found</t>
+          <t>Draft Recommendation</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -636,17 +636,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Engineering complete, legal verification pending</t>
+          <t>Engineering implementation available. Repository evidence reviewed. Formal legal validation pending.</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>profiles/employment_contract.json</t>
+          <t>ldv-backend/detector/profiles/employment_contract.json</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Active profile in CRA system. Engineering validation completed. Legal reviewer sign-off pending. (Notes: UU 13/2003 Ketenagakerjaan applies for ID.)</t>
+          <t>Engineering implementation available. Repository evidence reviewed. Formal legal validation pending. Legal approval pending. (Notes: UU 13/2003 Ketenagakerjaan applies for ID.)</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Standard Lease Agreement profile mapping required clauses.</t>
+          <t>A lease agreement is a contract whereby a lessor (landlord) grants the temporary use and occupancy of real or personal property to a lessee (tenant) in exchange for periodic rent payments.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">French civil-style code Art. Art. 1709, French Code civil Art. Art. 1719, KUH Perdata (Indonesian Civil Code) Art. Pasal 1338, French Code civil Art. Art. 1709, French Code civil Art. Art. 2288, French civil-style code Art. Art. 1719, KUHPerdata Art. Pasal 1550, French civil-style code Art. Art. 2288, KUH Perdata (Indonesian Civil Code) Art. Pasal 1338, UU No. 30 Tahun 1999 tentang Arbitrase dan Alternatif Penyelesaian Sengketa, KUHPerdata Art. Pasal 1548, KUH Perdata (Indonesian Civil Code) Art. Pasal 1320, Pasal 1338, KUHPerdata Art. Pasal 1820,  Art. </t>
+          <t>French Code civil Article Art. 2288, KUHPerdata Article Pasal 1820, French civil-style code Article Art. 1719, KUHPerdata Article Pasal 1550, French Code civil Article Art. 1709, French civil-style code Article Art. 1709, KUH Perdata (Indonesian Civil Code) Article Pasal 1338, UU No. 30 Tahun 1999 tentang Arbitrase dan Alternatif Penyelesaian Sengketa, French civil-style code Article Art. 2288, French Code civil Article Art. 1719, KUH Perdata (Indonesian Civil Code) Article Pasal 1338, KUHPerdata Article Pasal 1548, KUH Perdata (Indonesian Civil Code) Article Pasal 1320, Pasal 1338</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>lease agreement, rental agreement, tenancy agreement, property lease</t>
+          <t>tenancy agreement, lease agreement, property lease, rental agreement</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lease agreement grants temporary possession and use of property in exchange for rent, while construction contracts govern building or renovation work.</t>
+          <t>A lease agreement transfers the right of temporary possession and occupancy of real property in exchange for periodic rent payments. A construction contract governs building, renovation, or engineering work performed on property, with payment structures tied to structural deliverables. A general contract lacks real estate covenants and statutory tenant protections.</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Evidence Not Found</t>
+          <t>Draft Recommendation</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -753,17 +753,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Engineering complete, legal verification pending</t>
+          <t>Engineering implementation available. Repository evidence reviewed. Formal legal validation pending.</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>profiles/lease_agreement.json</t>
+          <t>ldv-backend/detector/profiles/lease_agreement.json</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Active profile in CRA system. Engineering validation completed. Legal reviewer sign-off pending. (Notes: )</t>
+          <t>Engineering implementation available. Repository evidence reviewed. Formal legal validation pending. Legal approval pending. (Notes: )</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Standard Software License Agreement profile mapping required clauses.</t>
+          <t>A software license is a legal agreement governing the use, distribution, or modification of software, defining the scope of rights granted by the licensor to the licensee.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">French Code de la propriété intellectuelle Art. Art. L111-1, Uniform Commercial Code Art. UCC 2-316, UU Hak Cipta Art. UU No. 28 Tahun 2014, KUHPerdata Art. Pasal 1491, KUH Perdata (Indonesian Civil Code) Art. Pasal 1338, UU No. 30 Tahun 1999 tentang Arbitrase dan Alternatif Penyelesaian Sengketa, KUH Perdata (Indonesian Civil Code) Art. Pasal 1338, KUH Perdata (Indonesian Civil Code) Art. Pasal 1243, Pasal 1365, French Code de la propriété intellectuelle Art. Art. L122-4, general law Art. IP ownership rules, general law Art. IP usage license, KUH Perdata (Indonesian Civil Code) Art. Pasal 1320, Pasal 1338, French Code civil Art. Art. 1643,  Art. </t>
+          <t>UU Hak Cipta Article UU No. 28 Tahun 2014, French Code de la propriété intellectuelle Article Art. L122-4, KUH Perdata (Indonesian Civil Code) Article Pasal 1243, Pasal 1365, French Code de la propriété intellectuelle Article Art. L111-1, KUHPerdata Article Pasal 1491, KUH Perdata (Indonesian Civil Code) Article Pasal 1338, UU No. 30 Tahun 1999 tentang Arbitrase dan Alternatif Penyelesaian Sengketa, Uniform Commercial Code Article UCC 2-316, KUH Perdata (Indonesian Civil Code) Article Pasal 1338, French Code civil Article Art. 1643, KUH Perdata (Indonesian Civil Code) Article Pasal 1320, Pasal 1338</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>software licence, EULA, software license agreement, license agreement, end user license agreement, software license, saas agreement, eula</t>
+          <t>software license agreement, software license, saas agreement, EULA, end user license agreement, software licence, eula, license agreement</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -840,12 +840,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>saas_agreement, it_services_contract</t>
+          <t>saas_agreement, it_service_agreement</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Software license governs installation/use of software code on user infrastructure, while SaaS agreement governs access to hosted cloud applications without code transfer.</t>
+          <t>A software license grants permission to install and run software code locally on the licensee's own hardware under a EULA. A SaaS agreement grants a subscription-based service right to access and use software hosted on the provider's remote servers without code transfer. An IT service agreement governs custom software development or system support tasks.</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Evidence Not Found</t>
+          <t>Draft Recommendation</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -870,17 +870,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Engineering complete, legal verification pending</t>
+          <t>Engineering implementation available. Repository evidence reviewed. Formal legal validation pending.</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>profiles/software_license.json</t>
+          <t>ldv-backend/detector/profiles/software_license.json</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Active profile in CRA system. Engineering validation completed. Legal reviewer sign-off pending. (Notes: )</t>
+          <t>Engineering implementation available. Repository evidence reviewed. Formal legal validation pending. Legal approval pending. (Notes: )</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Standard Service Agreement profile mapping required clauses.</t>
+          <t>A service agreement is a contract under which one party, the service provider, agrees to perform specific tasks or services for another party, the client, in exchange for fee-based compensation.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -932,12 +932,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">KUH Perdata (Indonesian Civil Code) Art. Pasal 1234, KUH Perdata (Indonesian Civil Code) Art. Pasal 1338, UU No. 30 Tahun 1999 tentang Arbitrase dan Alternatif Penyelesaian Sengketa, KUH Perdata (Indonesian Civil Code) Art. Pasal 1338, KUH Perdata (Indonesian Civil Code) Art. Pasal 1243, Pasal 1365, KUH Perdata (Indonesian Civil Code) Art. Pasal 1320, Pasal 1338,  Art. </t>
+          <t>KUH Perdata (Indonesian Civil Code) Article Pasal 1320, Pasal 1338, KUH Perdata (Indonesian Civil Code) Article Pasal 1243, Pasal 1365, KUH Perdata (Indonesian Civil Code) Article Pasal 1234, KUH Perdata (Indonesian Civil Code) Article Pasal 1338, KUH Perdata (Indonesian Civil Code) Article Pasal 1338, UU No. 30 Tahun 1999 tentang Arbitrase dan Alternatif Penyelesaian Sengketa</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>service agreement, services agreement, service contract, MSA, maintenance agreement, master services agreement</t>
+          <t>services agreement, maintenance agreement, service agreement, MSA, master services agreement, service contract</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>consulting_agreement, employment_contract, it_services_contract, general_contract</t>
+          <t>consulting_agreement, employment_contract, it_service_agreement, general_contract</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Service agreement is B2B for general tasks, consulting is for professional advisory, IT service is for technical systems, and employment involves direct master-servant subordination.</t>
+          <t>A service agreement is a standard commercial B2B contract for operational or physical tasks without employer subordination. A consulting agreement is restricted to expert professional advisory services. An IT service agreement is specialized for technical environments (including SLAs and infrastructure management). An employment contract creates a master-servant relationship subject to labor law.</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Evidence Not Found</t>
+          <t>Draft Recommendation</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -987,17 +987,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Engineering complete, legal verification pending</t>
+          <t>Engineering implementation available. Repository evidence reviewed. Formal legal validation pending.</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>profiles/service_agreement.json</t>
+          <t>ldv-backend/detector/profiles/service_agreement.json</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Active profile in CRA system. Engineering validation completed. Legal reviewer sign-off pending. (Notes: )</t>
+          <t>Engineering implementation available. Repository evidence reviewed. Formal legal validation pending. Legal approval pending. (Notes: )</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Standard Consulting Agreement profile mapping required clauses.</t>
+          <t>A consulting agreement is a contract whereby an independent consultant agrees to provide expert advisory or professional services to a client on a non-subordinate, project-specific basis.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">KUH Perdata (Indonesian Civil Code) Art. Pasal 1234, KUH Perdata (Indonesian Civil Code) Art. Pasal 1338, UU No. 30 Tahun 1999 tentang Arbitrase dan Alternatif Penyelesaian Sengketa, KUH Perdata (Indonesian Civil Code) Art. Pasal 1338, KUH Perdata (Indonesian Civil Code) Art. Pasal 1320, Pasal 1338, KUH Perdata (Indonesian Civil Code) Art. Pasal 1338, UU No. 30 Tahun 2000 tentang Rahasia Dagang,  Art. </t>
+          <t>KUH Perdata (Indonesian Civil Code) Article Pasal 1320, Pasal 1338, KUH Perdata (Indonesian Civil Code) Article Pasal 1338, UU No. 30 Tahun 2000 tentang Rahasia Dagang, KUH Perdata (Indonesian Civil Code) Article Pasal 1234, KUH Perdata (Indonesian Civil Code) Article Pasal 1338, KUH Perdata (Indonesian Civil Code) Article Pasal 1338, UU No. 30 Tahun 1999 tentang Arbitrase dan Alternatif Penyelesaian Sengketa</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>consulting agreement, consultancy agreement, advisory agreement</t>
+          <t>advisory agreement, consultancy agreement, consulting agreement</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Consulting is for professional advisory services on an independent contractor basis without direct supervision or employment benefits.</t>
+          <t>A consulting agreement is restricted to expert professional advisory services. The consultant acts as an independent business entity providing professional advice without subordination, integration into the client's organizational hierarchy, or statutory employment benefits.</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Evidence Not Found</t>
+          <t>Draft Recommendation</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1104,17 +1104,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Engineering complete, legal verification pending</t>
+          <t>Engineering implementation available. Repository evidence reviewed. Formal legal validation pending.</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>profiles/consulting_agreement.json</t>
+          <t>ldv-backend/detector/profiles/consulting_agreement.json</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Active profile in CRA system. Engineering validation completed. Legal reviewer sign-off pending. (Notes: )</t>
+          <t>Engineering implementation available. Repository evidence reviewed. Formal legal validation pending. Legal approval pending. (Notes: )</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Standard Commercial Agreement profile mapping required clauses.</t>
+          <t>A commercial agreement is a business-to-business contract defining trade, supply, or operational terms under which commercial entities execute commercial transactions.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1166,12 +1166,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">KUH Perdata (Indonesian Civil Code) Art. Pasal 1234, KUH Perdata (Indonesian Civil Code) Art. Pasal 1338, UU No. 30 Tahun 1999 tentang Arbitrase dan Alternatif Penyelesaian Sengketa, KUH Perdata (Indonesian Civil Code) Art. Pasal 1338, KUH Perdata (Indonesian Civil Code) Art. Pasal 1243, Pasal 1365, KUH Perdata (Indonesian Civil Code) Art. Pasal 1320, Pasal 1338,  Art. </t>
+          <t>KUH Perdata (Indonesian Civil Code) Article Pasal 1243, Pasal 1365, KUH Perdata (Indonesian Civil Code) Article Pasal 1338, UU No. 30 Tahun 1999 tentang Arbitrase dan Alternatif Penyelesaian Sengketa, KUH Perdata (Indonesian Civil Code) Article Pasal 1234, KUH Perdata (Indonesian Civil Code) Article Pasal 1338, KUH Perdata (Indonesian Civil Code) Article Pasal 1320, Pasal 1338</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>trade agreement, commercial agreement, commercial contract, business agreement</t>
+          <t>commercial contract, commercial agreement, business agreement, trade agreement</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Commercial agreement covers trade, business operations, and supply terms between businesses, broader than purchase/service agreements but narrower than general contracts.</t>
+          <t>A commercial agreement is a B2B contract governing commercial relations (like distribution or ongoing supply). It is narrower than a general contract (no specific commercial context) but broader than purchase agreements (tangible goods transfer) or service agreements (pure labor execution).</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Evidence Not Found</t>
+          <t>Draft Recommendation</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1221,17 +1221,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Engineering complete, legal verification pending</t>
+          <t>Engineering implementation available. Repository evidence reviewed. Formal legal validation pending.</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>profiles/commercial_agreement.json</t>
+          <t>ldv-backend/detector/profiles/commercial_agreement.json</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Active profile in CRA system. Engineering validation completed. Legal reviewer sign-off pending. (Notes: )</t>
+          <t>Engineering implementation available. Repository evidence reviewed. Formal legal validation pending. Legal approval pending. (Notes: )</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Standard Non-Disclosure Agreement profile mapping required clauses.</t>
+          <t>A non-disclosure agreement is a contract under which parties agree to maintain the confidentiality of proprietary information shared between them and restrict its unauthorized use or disclosure.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1283,12 +1283,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>KUHPerdata Art. Pasal 1338, KUH Perdata (Indonesian Civil Code) Art. Pasal 1338, UU No. 30 Tahun 1999 tentang Arbitrase dan Alternatif Penyelesaian Sengketa, KUH Perdata (Indonesian Civil Code) Art. Pasal 1338,  Art. , KUH Perdata (Indonesian Civil Code) Art. Pasal 1320, Pasal 1338, KUH Perdata (Indonesian Civil Code) Art. Pasal 1338, UU No. 30 Tahun 2000 tentang Rahasia Dagang, French Code civil Art. Art. 1134, general law Art. Return of materials</t>
+          <t>KUH Perdata (Indonesian Civil Code) Article Pasal 1338, UU No. 30 Tahun 2000 tentang Rahasia Dagang, French Code civil Article Art. 1134, KUH Perdata (Indonesian Civil Code) Article Pasal 1338, UU No. 30 Tahun 1999 tentang Arbitrase dan Alternatif Penyelesaian Sengketa, KUHPerdata Article Pasal 1338, KUH Perdata (Indonesian Civil Code) Article Pasal 1338, KUH Perdata (Indonesian Civil Code) Article Pasal 1320, Pasal 1338</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>confidentiality agreement, geheimhouding, nda, NDA, non-disclosure agreement</t>
+          <t>non-disclosure agreement, confidentiality agreement, geheimhouding, nda, NDA</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Non-disclosure agreement is dedicated entirely to protecting proprietary information and trade secrets, whereas general contracts contain confidentiality as a secondary term.</t>
+          <t>A non-disclosure agreement is a contract whose sole and essential object is the protection of proprietary information and trade secrets. General contracts include confidentiality clauses as ancillary terms subordinate to the main transaction (e.g. sale, service).</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Evidence Not Found</t>
+          <t>Draft Recommendation</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Engineering complete, legal verification pending</t>
+          <t>Engineering implementation available. Repository evidence reviewed. Formal legal validation pending.</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>profiles/non_disclosure_agreement.json</t>
+          <t>ldv-backend/detector/profiles/non_disclosure_agreement.json</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Active profile in CRA system. Engineering validation completed. Legal reviewer sign-off pending. (Notes: )</t>
+          <t>Engineering implementation available. Repository evidence reviewed. Formal legal validation pending. Legal approval pending. (Notes: )</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Standard Loan Agreement profile mapping required clauses.</t>
+          <t>A loan agreement is a contract whereby a lender transfers a principal sum of money to a borrower, who agrees to repay the principal along with agreed-upon interest according to a specified schedule.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">KUH Perdata (Indonesian Civil Code) Art. Pasal 1234, KUH Perdata (Indonesian Civil Code) Art. Pasal 1338, UU No. 30 Tahun 1999 tentang Arbitrase dan Alternatif Penyelesaian Sengketa, KUH Perdata (Indonesian Civil Code) Art. Pasal 1338, KUHPerdata Art. Pasal 1238, general law Art. Default provisions, French Code civil Art. Art. 1224, KUH Perdata (Indonesian Civil Code) Art. Pasal 1320, Pasal 1338,  Art. </t>
+          <t>French Code civil Article Art. 1224, KUHPerdata Article Pasal 1238, KUH Perdata (Indonesian Civil Code) Article Pasal 1338, UU No. 30 Tahun 1999 tentang Arbitrase dan Alternatif Penyelesaian Sengketa, KUH Perdata (Indonesian Civil Code) Article Pasal 1234, KUH Perdata (Indonesian Civil Code) Article Pasal 1338, KUH Perdata (Indonesian Civil Code) Article Pasal 1320, Pasal 1338</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>loan agreement, creditor agreement, credit agreement, loan contract</t>
+          <t>loan contract, loan agreement, creditor agreement, credit agreement</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Loan agreement specifically governs the lending of principal funds from a lender to a borrower with repayment schedules and interest rates.</t>
+          <t>A loan agreement is a financial contract whose essential purpose is the provision of credit, defining the transfer of a principal sum of money and the borrower's absolute obligation to repay it with interest. General commercial contracts may contain payment schedules or trade credit terms but do not involve the lending of financial principal.</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Evidence Not Found</t>
+          <t>Draft Recommendation</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1455,17 +1455,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>Engineering complete, legal verification pending</t>
+          <t>Engineering implementation available. Repository evidence reviewed. Formal legal validation pending.</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>profiles/loan_agreement.json</t>
+          <t>ldv-backend/detector/profiles/loan_agreement.json</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Active profile in CRA system. Engineering validation completed. Legal reviewer sign-off pending. (Notes: )</t>
+          <t>Engineering implementation available. Repository evidence reviewed. Formal legal validation pending. Legal approval pending. (Notes: )</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Standard Partnership Agreement profile mapping required clauses.</t>
+          <t>A partnership agreement is a contract establishing a co-ownership structure under which two or more partners agree to pool resources and share the profits, losses, and management responsibilities of a business venture.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1517,12 +1517,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">French civil-style code Art. Art. 1832, general law Art. Management rights, KUH Perdata (Indonesian Civil Code) Art. Pasal 1338, UU No. 30 Tahun 1999 tentang Arbitrase dan Alternatif Penyelesaian Sengketa, KUH Perdata (Indonesian Civil Code) Art. Pasal 1338, French Code civil Art. Art. 1852, KUHPerdata Art. Pasal 1636, KUH Perdata (Indonesian Civil Code) Art. Pasal 1320, Pasal 1338, KUHPerdata Art. Pasal 1618, French Code civil Art. Art. 1832,  Art. </t>
+          <t>KUHPerdata Article Pasal 1636, French Code civil Article Art. 1852, French civil-style code Article Art. 1832, KUH Perdata (Indonesian Civil Code) Article Pasal 1338, UU No. 30 Tahun 1999 tentang Arbitrase dan Alternatif Penyelesaian Sengketa, KUHPerdata Article Pasal 1618, French Code civil Article Art. 1832, KUH Perdata (Indonesian Civil Code) Article Pasal 1338, KUH Perdata (Indonesian Civil Code) Article Pasal 1320, Pasal 1338</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>joint venture, joint venture agreement, partnership agreement, partnership contract</t>
+          <t>joint venture agreement, partnership contract, joint venture, partnership agreement</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Partnership agreement establishes an ongoing co-ownership structure to share profits and losses, whereas joint ventures are typically project-specific.</t>
+          <t>A partnership agreement establishes an ongoing co-ownership structure under which partners agree to pool resources and share all profits, losses, and management responsibilities of a business. A joint venture agreement is project-specific and does not create a permanent co-ownership entity.</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Evidence Not Found</t>
+          <t>Draft Recommendation</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1572,17 +1572,17 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Engineering complete, legal verification pending</t>
+          <t>Engineering implementation available. Repository evidence reviewed. Formal legal validation pending.</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>profiles/partnership_agreement.json</t>
+          <t>ldv-backend/detector/profiles/partnership_agreement.json</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Active profile in CRA system. Engineering validation completed. Legal reviewer sign-off pending. (Notes: )</t>
+          <t>Engineering implementation available. Repository evidence reviewed. Formal legal validation pending. Legal approval pending. (Notes: )</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Standard Purchase Agreement profile mapping required clauses.</t>
+          <t>A purchase agreement is a contract whereby a seller transfers or agrees to transfer the ownership of physical goods or assets to a buyer in exchange for a specified monetary payment.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1634,17 +1634,17 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">KUH Perdata (Indonesian Civil Code) Art. Pasal 1234, Uniform Commercial Code Art. UCC 2-201, Uniform Commercial Code Art. UCC 2-401, KUH Perdata (Indonesian Civil Code) Art. Pasal 1338, KUH Perdata (Indonesian Civil Code) Art. Pasal 1338, UU No. 30 Tahun 1999 tentang Arbitrase dan Alternatif Penyelesaian Sengketa, KUHPerdata Art. Pasal 1459, French Code civil Art. Art. 1583, KUHPerdata Art. Pasal 1457, KUH Perdata (Indonesian Civil Code) Art. Pasal 1320, Pasal 1338,  Art. </t>
+          <t>French Code civil Article Art. 1583, KUH Perdata (Indonesian Civil Code) Article Pasal 1320, Pasal 1338, KUH Perdata (Indonesian Civil Code) Article Pasal 1338, UU No. 30 Tahun 1999 tentang Arbitrase dan Alternatif Penyelesaian Sengketa, Uniform Commercial Code Article UCC 2-401, KUHPerdata Article Pasal 1459, KUHPerdata Article Pasal 1457, KUH Perdata (Indonesian Civil Code) Article Pasal 1338, Uniform Commercial Code Article UCC 2-201, KUH Perdata (Indonesian Civil Code) Article Pasal 1234</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>sales contract, sale agreement, purchase agreement</t>
+          <t>purchase agreement, sales contract, sale agreement</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>perjanjian pembelian, perjanjian jual beli</t>
+          <t>perjanjian jual beli, perjanjian pembelian</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Purchase agreement governs the transfer of ownership of physical goods or assets in exchange for payment, including delivery terms and product warranties.</t>
+          <t>A purchase agreement is legally defined by the transfer of title and ownership of specific tangible goods or assets in exchange for price. A service agreement transfers the utility of labor, and a commercial agreement covers broader distribution or trade partnerships.</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Evidence Not Found</t>
+          <t>Draft Recommendation</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1689,17 +1689,17 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Engineering complete, legal verification pending</t>
+          <t>Engineering implementation available. Repository evidence reviewed. Formal legal validation pending.</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>profiles/purchase_agreement.json</t>
+          <t>ldv-backend/detector/profiles/purchase_agreement.json</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Active profile in CRA system. Engineering validation completed. Legal reviewer sign-off pending. (Notes: )</t>
+          <t>Engineering implementation available. Repository evidence reviewed. Formal legal validation pending. Legal approval pending. (Notes: )</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Standard General Contract profile mapping required baseline clauses.</t>
+          <t>A general contract is a baseline legal agreement establishing mutual covenants and obligations between contracting parties, serving as a fallback for transactions not covered by specialized contract types.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1751,17 +1751,17 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">KUH Perdata (Indonesian Civil Code) Art. Pasal 1234, KUH Perdata (Indonesian Civil Code) Art. Pasal 1338, UU No. 30 Tahun 1999 tentang Arbitrase dan Alternatif Penyelesaian Sengketa, KUH Perdata (Indonesian Civil Code) Art. Pasal 1338, KUH Perdata (Indonesian Civil Code) Art. Pasal 1243, Pasal 1365, KUH Perdata (Indonesian Civil Code) Art. Pasal 1320, Pasal 1338,  Art. </t>
+          <t>KUH Perdata (Indonesian Civil Code) Article Pasal 1243, Pasal 1365, KUH Perdata (Indonesian Civil Code) Article Pasal 1338, UU No. 30 Tahun 1999 tentang Arbitrase dan Alternatif Penyelesaian Sengketa, KUH Perdata (Indonesian Civil Code) Article Pasal 1234, KUH Perdata (Indonesian Civil Code) Article Pasal 1338, KUH Perdata (Indonesian Civil Code) Article Pasal 1320, Pasal 1338</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>contract, general agreement, agreement, general contract</t>
+          <t>general agreement, general contract, contract, agreement</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>kontrak, perjanjian umum, perjanjian, kontrak umum</t>
+          <t>kontrak, kontrak umum, perjanjian, perjanjian umum</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>General contract is a baseline agreement used when the transaction does not fit into any specialized category.</t>
+          <t>A general contract is a baseline agreement that establishes mutual covenants without specializing in any trade, service, employment, or property lease category.</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Evidence Not Found</t>
+          <t>Draft Recommendation</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1806,17 +1806,17 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Engineering complete, legal verification pending</t>
+          <t>Engineering implementation available. Repository evidence reviewed. Formal legal validation pending.</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>profiles/general_contract.json</t>
+          <t>ldv-backend/detector/profiles/general_contract.json</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Active profile in CRA system. Engineering validation completed. Legal reviewer sign-off pending. (Notes: Fallback profile.)</t>
+          <t>Engineering implementation available. Repository evidence reviewed. Formal legal validation pending. Legal approval pending. (Notes: Fallback profile.)</t>
         </is>
       </c>
     </row>
